--- a/week-01/Ex4B_more_GTrends.xlsx
+++ b/week-01/Ex4B_more_GTrends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\myleahrichardson\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA8B1FE3-C834-4AA0-86C5-BBEDF09C2B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BF6D3B-6C61-4FDF-9F76-20C41AC47DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{1BBCD816-9215-4E1B-A844-DA072B378BE5}"/>
   </bookViews>
@@ -1256,7 +1256,9 @@
       <c r="C10" s="1">
         <v>0.56999999999999995</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1">
+        <v>0.2</v>
+      </c>
       <c r="E10" s="1">
         <v>0.23</v>
       </c>
@@ -1761,7 +1763,13 @@
       <c r="B40" t="s">
         <v>1</v>
       </c>
+      <c r="C40" s="1">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="D40" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E40" s="1">
         <v>0.18</v>
       </c>
     </row>
@@ -1772,6 +1780,15 @@
       <c r="B41" t="s">
         <v>2</v>
       </c>
+      <c r="C41" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0.14000000000000001</v>
+      </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
@@ -1783,6 +1800,9 @@
       <c r="C42" s="1">
         <v>0.56999999999999995</v>
       </c>
+      <c r="D42" s="1">
+        <v>0.18</v>
+      </c>
       <c r="E42" s="1">
         <v>0.18</v>
       </c>
@@ -1958,31 +1978,17 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C53" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="D53" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E53" s="1">
-        <v>0.18</v>
-      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C54" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="D54" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="E54" s="1">
-        <v>0.17</v>
-      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D55" s="1">
-        <v>0.24</v>
-      </c>
+      <c r="D55" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E55" xr:uid="{40D38EDE-2DE9-487B-BCCB-5BC160749F87}"/>
@@ -2272,6 +2278,12 @@
       <c r="AM2" s="1">
         <v>0.63</v>
       </c>
+      <c r="AN2" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>0.68</v>
+      </c>
       <c r="AP2" s="1">
         <v>0.56999999999999995</v>
       </c>
@@ -2305,12 +2317,8 @@
       <c r="AZ2" s="1">
         <v>0.68</v>
       </c>
-      <c r="BA2" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="BB2" s="1">
-        <v>0.59</v>
-      </c>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -2340,7 +2348,9 @@
       <c r="I3" s="1">
         <v>0.24</v>
       </c>
-      <c r="J3" s="1"/>
+      <c r="J3" s="1">
+        <v>0.2</v>
+      </c>
       <c r="K3" s="1">
         <v>0.2</v>
       </c>
@@ -2431,6 +2441,12 @@
       <c r="AN3" s="1">
         <v>0.18</v>
       </c>
+      <c r="AO3" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>0.18</v>
+      </c>
       <c r="AQ3" s="1">
         <v>0.25</v>
       </c>
@@ -2461,15 +2477,9 @@
       <c r="AZ3" s="1">
         <v>0.22</v>
       </c>
-      <c r="BA3" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="BB3" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="BC3" s="1">
-        <v>0.24</v>
-      </c>
+      <c r="BA3" s="1"/>
+      <c r="BB3" s="1"/>
+      <c r="BC3" s="1"/>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -2589,6 +2599,12 @@
       <c r="AM4" s="1">
         <v>0.19</v>
       </c>
+      <c r="AN4" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
       <c r="AP4" s="1">
         <v>0.18</v>
       </c>
@@ -2622,12 +2638,8 @@
       <c r="AZ4" s="1">
         <v>0.18</v>
       </c>
-      <c r="BA4" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="BB4" s="1">
-        <v>0.17</v>
-      </c>
+      <c r="BA4" s="1"/>
+      <c r="BB4" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
